--- a/TestData/TMTI0054719_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnCFOpportunityAndEngagementPage.xlsx
+++ b/TestData/TMTI0054719_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnCFOpportunityAndEngagementPage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA40B293-F5AC-4C3F-AE4D-4ABFBBEC1485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C7FACE-FE5B-4346-AB89-049424EBBCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{D381DC3E-0C7A-48CF-8E3B-36CB765DCADA}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D381DC3E-0C7A-48CF-8E3B-36CB765DCADA}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -140,9 +140,6 @@
     <t>Buyside</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -270,6 +267,9 @@
   </si>
   <si>
     <t>Engagements</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -338,9 +338,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -378,7 +378,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -484,7 +484,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -626,7 +626,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -635,9 +635,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7DDA40C-CB43-498D-A2ED-A0851564593B}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -729,7 +729,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -740,85 +740,85 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" t="s">
         <v>32</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>33</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
         <v>34</v>
       </c>
-      <c r="G2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" t="s">
         <v>35</v>
       </c>
-      <c r="I2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>36</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>37</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>38</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="R2" t="s">
         <v>39</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="S2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="P2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="U2" t="s">
         <v>40</v>
       </c>
-      <c r="S2" t="s">
-        <v>40</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>41</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>42</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>43</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>44</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>45</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD2" t="s">
         <v>46</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -829,19 +829,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6978B76C-41D6-4CB8-BB5A-CE3CBB65EA6D}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -852,24 +852,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1988A2C0-E26B-4053-9887-74900EAFFAF5}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -880,26 +880,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A3F6A9-43ED-49B3-9AC1-A223C8D04358}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -910,58 +910,58 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4922F08E-3E13-47AA-BD27-63BC12B6D061}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>58</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>59</v>
-      </c>
-      <c r="D2" t="s">
-        <v>60</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -972,24 +972,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B9F0D-8652-479A-903D-887FA1C2C103}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1000,24 +1000,24 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81393CD3-5435-4B58-8311-A4C2E7A02EB9}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTI0054719_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnCFOpportunityAndEngagementPage.xlsx
+++ b/TestData/TMTI0054719_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnCFOpportunityAndEngagementPage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C7FACE-FE5B-4346-AB89-049424EBBCF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF93F4A0-F0A2-4E64-8188-4F03A2A93A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D381DC3E-0C7A-48CF-8E3B-36CB765DCADA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{D381DC3E-0C7A-48CF-8E3B-36CB765DCADA}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="77">
   <si>
     <t>Client</t>
   </si>
@@ -188,9 +188,6 @@
     <t>CaoUser</t>
   </si>
   <si>
-    <t>Meissa Lee</t>
-  </si>
-  <si>
     <t>Contact</t>
   </si>
   <si>
@@ -270,6 +267,12 @@
   </si>
   <si>
     <t>Business Services</t>
+  </si>
+  <si>
+    <t>James Craven</t>
+  </si>
+  <si>
+    <t>Gemma Hardy</t>
   </si>
 </sst>
 </file>
@@ -740,7 +743,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
@@ -773,13 +776,13 @@
         <v>38</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R2" t="s">
         <v>39</v>
@@ -788,7 +791,7 @@
         <v>39</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U2" t="s">
         <v>40</v>
@@ -809,10 +812,10 @@
         <v>45</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AC2" t="s">
         <v>38</v>
@@ -836,12 +839,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -859,17 +862,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -882,8 +885,8 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -896,10 +899,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -914,28 +917,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -943,25 +946,25 @@
         <v>41</v>
       </c>
       <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
         <v>57</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>58</v>
-      </c>
-      <c r="D2" t="s">
-        <v>59</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -979,17 +982,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1007,17 +1010,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTI0054719_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnCFOpportunityAndEngagementPage.xlsx
+++ b/TestData/TMTI0054719_VerificationOfNewFieldAssociatedOpportunityAvailabiltyAndFunctionalityOnCFOpportunityAndEngagementPage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA40B293-F5AC-4C3F-AE4D-4ABFBBEC1485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF93F4A0-F0A2-4E64-8188-4F03A2A93A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{D381DC3E-0C7A-48CF-8E3B-36CB765DCADA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{D381DC3E-0C7A-48CF-8E3B-36CB765DCADA}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="77">
   <si>
     <t>Client</t>
   </si>
@@ -140,9 +140,6 @@
     <t>Buyside</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -191,9 +188,6 @@
     <t>CaoUser</t>
   </si>
   <si>
-    <t>Meissa Lee</t>
-  </si>
-  <si>
     <t>Contact</t>
   </si>
   <si>
@@ -270,6 +264,15 @@
   </si>
   <si>
     <t>Engagements</t>
+  </si>
+  <si>
+    <t>Business Services</t>
+  </si>
+  <si>
+    <t>James Craven</t>
+  </si>
+  <si>
+    <t>Gemma Hardy</t>
   </si>
 </sst>
 </file>
@@ -338,9 +341,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -378,7 +381,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -484,7 +487,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -626,7 +629,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -635,9 +638,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7DDA40C-CB43-498D-A2ED-A0851564593B}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -729,7 +732,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -740,85 +743,85 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
         <v>32</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>33</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
         <v>34</v>
       </c>
-      <c r="G2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" t="s">
         <v>35</v>
       </c>
-      <c r="I2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>36</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>37</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>38</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R2" t="s">
         <v>39</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="U2" t="s">
         <v>40</v>
       </c>
-      <c r="S2" t="s">
-        <v>40</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>41</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>42</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>43</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>44</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>45</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD2" t="s">
         <v>46</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -829,19 +832,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6978B76C-41D6-4CB8-BB5A-CE3CBB65EA6D}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -852,24 +855,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1988A2C0-E26B-4053-9887-74900EAFFAF5}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -880,26 +883,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A3F6A9-43ED-49B3-9AC1-A223C8D04358}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -910,58 +913,58 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4922F08E-3E13-47AA-BD27-63BC12B6D061}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="C2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>58</v>
-      </c>
-      <c r="C2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" t="s">
-        <v>60</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -972,24 +975,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B9F0D-8652-479A-903D-887FA1C2C103}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1000,24 +1003,24 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81393CD3-5435-4B58-8311-A4C2E7A02EB9}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
